--- a/docs/build/lakeshore-enterprise-context/source/04_finance_performance/working_capital_drivers.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/04_finance_performance/working_capital_drivers.xlsx
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>73.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="5">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>47.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>66.7</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="7">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n">
         <v>56</v>
       </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
       <c r="D7" t="n">
-        <v>13.6</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
